--- a/data/trans_orig/IP2905_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP2905_2023-Edad-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20800</t>
+          <t>20871</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31289</t>
+          <t>30920</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15590</t>
+          <t>15071</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25866</t>
+          <t>25643</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38983</t>
+          <t>39184</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53045</t>
+          <t>53678</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,88%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15721</t>
+          <t>16090</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26210</t>
+          <t>26139</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19856</t>
+          <t>20079</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30132</t>
+          <t>30651</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39687</t>
+          <t>39054</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53749</t>
+          <t>53548</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,74%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65140</t>
+          <t>65398</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87181</t>
+          <t>86356</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97911</t>
+          <t>97960</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>145475</t>
+          <t>146286</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>177315</t>
+          <t>177742</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,29%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71702</t>
+          <t>72527</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93743</t>
+          <t>93485</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>83137</t>
+          <t>83088</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>162616</t>
+          <t>162189</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>194456</t>
+          <t>193645</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>56,97%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76191</t>
+          <t>74530</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99648</t>
+          <t>97760</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99052</t>
+          <t>98749</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>127398</t>
+          <t>126105</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>181183</t>
+          <t>181368</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>219900</t>
+          <t>217953</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>56,76%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71880</t>
+          <t>73768</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95337</t>
+          <t>96998</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85092</t>
+          <t>86385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>113438</t>
+          <t>113741</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>164118</t>
+          <t>166065</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>202835</t>
+          <t>202650</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,77%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>105298</t>
+          <t>103519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133468</t>
+          <t>133311</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>138118</t>
+          <t>135463</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>179939</t>
+          <t>177085</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>248636</t>
+          <t>250544</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>297808</t>
+          <t>302820</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>55,98%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>107676</t>
+          <t>107833</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135846</t>
+          <t>137625</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119845</t>
+          <t>122699</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>161666</t>
+          <t>164321</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>243120</t>
+          <t>238108</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>292292</t>
+          <t>290384</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,68%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>284750</t>
+          <t>286377</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>328568</t>
+          <t>329456</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>347770</t>
+          <t>348861</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>404953</t>
+          <t>404445</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>648831</t>
+          <t>646341</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>719338</t>
+          <t>719224</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,98%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>289997</t>
+          <t>289109</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>333815</t>
+          <t>332188</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>334091</t>
+          <t>334599</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>391274</t>
+          <t>390183</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>638271</t>
+          <t>638385</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>708778</t>
+          <t>711268</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,39%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2905_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP2905_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17265</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13191</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21880</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>45,66%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>34,89%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>57,87%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>25714</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20871</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>30920</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>54,7%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>44,4%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>65,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20543</t>
+          <t>23436</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15071</t>
+          <t>18866</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25643</t>
+          <t>28137</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>46257</t>
+          <t>40701</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39184</t>
+          <t>34108</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53678</t>
+          <t>47832</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>59,18%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20545</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15930</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24619</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>54,34%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>42,13%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>65,11%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>21296</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16090</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>26139</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>45,3%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>34,23%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>55,6%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25179</t>
+          <t>19581</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20079</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30651</t>
+          <t>24151</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>46475</t>
+          <t>40126</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39054</t>
+          <t>32995</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53548</t>
+          <t>46719</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,8%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37810</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37810</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37810</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>47010</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>47010</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>47010</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45722</t>
+          <t>43017</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45722</t>
+          <t>43017</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45722</t>
+          <t>43017</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>92732</t>
+          <t>80827</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>92732</t>
+          <t>80827</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>92732</t>
+          <t>80827</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>73510</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>63678</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>83171</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>47,03%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>40,74%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>53,21%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>76213</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>65398</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>86356</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>47,97%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>41,16%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>54,35%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86133</t>
+          <t>71804</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74615</t>
+          <t>62139</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97960</t>
+          <t>80842</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>162347</t>
+          <t>145314</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>146286</t>
+          <t>130891</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>177742</t>
+          <t>159943</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>53,06%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>82791</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>73130</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>92623</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>52,97%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>46,79%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>59,26%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>82670</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>72527</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>93485</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>52,03%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>45,65%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>58,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>94915</t>
+          <t>73355</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>83088</t>
+          <t>64317</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106433</t>
+          <t>83020</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>177584</t>
+          <t>156147</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>162189</t>
+          <t>141518</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>193645</t>
+          <t>170570</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,58%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156301</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156301</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156301</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>158883</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>158883</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>158883</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181048</t>
+          <t>145159</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181048</t>
+          <t>145159</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181048</t>
+          <t>145159</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>339931</t>
+          <t>301461</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>339931</t>
+          <t>301461</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>339931</t>
+          <t>301461</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>101973</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>88935</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>114572</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>50,95%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>44,44%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>57,25%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>87016</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>74530</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>97760</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>50,73%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>43,45%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>56,99%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>113215</t>
+          <t>88044</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98749</t>
+          <t>75457</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>126105</t>
+          <t>98504</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>200231</t>
+          <t>190017</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>181368</t>
+          <t>172032</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>217953</t>
+          <t>207922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>55,71%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84512</t>
+          <t>98153</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73768</t>
+          <t>85554</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>96998</t>
+          <t>111191</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>99275</t>
+          <t>85062</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86385</t>
+          <t>74602</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>113741</t>
+          <t>97649</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>183787</t>
+          <t>183215</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>166065</t>
+          <t>165310</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>202650</t>
+          <t>201200</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>53,91%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>171528</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>171528</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>171528</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173106</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173106</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173106</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>384018</t>
+          <t>373232</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>384018</t>
+          <t>373232</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>384018</t>
+          <t>373232</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>150347</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>133233</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>170716</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>52,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>46,41%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>59,46%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>118129</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>103519</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>133311</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>48,99%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>42,93%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>55,28%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>156190</t>
+          <t>115866</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>135463</t>
+          <t>101969</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>177085</t>
+          <t>129375</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>274319</t>
+          <t>266212</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>250544</t>
+          <t>241555</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>302820</t>
+          <t>291248</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>54,68%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>136757</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>116388</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>153871</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>47,63%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>40,54%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>53,59%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>123015</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>107833</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>137625</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>51,01%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>44,72%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>57,07%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>143594</t>
+          <t>129628</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>122699</t>
+          <t>116119</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>164321</t>
+          <t>143525</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>266609</t>
+          <t>266386</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>238108</t>
+          <t>241350</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>290384</t>
+          <t>291043</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>54,65%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>287104</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>287104</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>287104</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>333</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>241144</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>241144</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>241144</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>299784</t>
+          <t>245494</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>299784</t>
+          <t>245494</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>299784</t>
+          <t>245494</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>540928</t>
+          <t>532598</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>540928</t>
+          <t>532598</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>540928</t>
+          <t>532598</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>343094</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>318777</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>369021</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>50,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>46,79%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>54,16%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>448</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>307072</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>286377</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>329456</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>49,64%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>46,3%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>53,26%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>376082</t>
+          <t>299151</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>348861</t>
+          <t>278773</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>404445</t>
+          <t>321070</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>683154</t>
+          <t>642245</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>646341</t>
+          <t>610007</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>719224</t>
+          <t>672454</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,2%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>457</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>338247</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>312320</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>362564</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>49,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>45,84%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>53,21%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>458</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>311493</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>289109</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>332188</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>50,36%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>46,74%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>53,7%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>457</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>362962</t>
+          <t>307626</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>334599</t>
+          <t>285707</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>390183</t>
+          <t>328004</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>674455</t>
+          <t>645872</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>638385</t>
+          <t>615663</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>711268</t>
+          <t>678110</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,64%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>681341</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>681341</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>681341</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>906</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>618565</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>618565</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>618565</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>932</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>739044</t>
+          <t>606777</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>739044</t>
+          <t>606777</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>739044</t>
+          <t>606777</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1357609</t>
+          <t>1288117</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1357609</t>
+          <t>1288117</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1357609</t>
+          <t>1288117</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
